--- a/data/trans_orig/Q45B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>42050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48067</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1018045</t>
+          <t>1018823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1028828</t>
+          <t>1028994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1271940</t>
+          <t>1271545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1294167</t>
+          <t>1293788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2309544</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2296635</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2320475</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>98,41%</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2293</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2309544</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>2296297</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2320106</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>17725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>25896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22126</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44615</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140075</t>
+          <t>137240</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186639</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166804</t>
+          <t>166324</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>218787</t>
+          <t>219428</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1640037</t>
+          <t>1642330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1665465</t>
+          <t>1665900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1391518</t>
+          <t>1392522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1438588</t>
+          <t>1442646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3044658</t>
+          <t>3044188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3099780</t>
+          <t>3099511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47353</t>
+          <t>48505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76980</t>
+          <t>76688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>64424</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100292</t>
+          <t>101270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>518668</t>
+          <t>518763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>538776</t>
+          <t>538787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396700</t>
+          <t>398331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>427590</t>
+          <t>427278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>923449</t>
+          <t>923703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>960458</t>
+          <t>960657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72690</t>
+          <t>71108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>222005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>282271</t>
+          <t>284702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272474</t>
+          <t>274280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>343549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3193555</t>
+          <t>3192980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3227215</t>
+          <t>3226611</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3083760</t>
+          <t>3080756</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3145380</t>
+          <t>3144442</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6287720</t>
+          <t>6287354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6363238</t>
+          <t>6360052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>32281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59780</t>
+          <t>58069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>944712</t>
+          <t>945225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>961602</t>
+          <t>961071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1286952</t>
+          <t>1285972</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1310405</t>
+          <t>1309346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2237626</t>
+          <t>2240123</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2267909</t>
+          <t>2267237</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37293</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>32001</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60596</t>
+          <t>60279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>117084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>161222</t>
+          <t>162481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157079</t>
+          <t>157796</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>212240</t>
+          <t>212601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1888858</t>
+          <t>1888551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1918354</t>
+          <t>1918939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1569643</t>
+          <t>1568995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1616735</t>
+          <t>1617679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3467950</t>
+          <t>3467840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3525415</t>
+          <t>3526341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50521</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80478</t>
+          <t>80817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65488</t>
+          <t>65744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103839</t>
+          <t>103734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>450513</t>
+          <t>450208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469227</t>
+          <t>469441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366258</t>
+          <t>366524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>398589</t>
+          <t>400603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>821664</t>
+          <t>824318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>861487</t>
+          <t>861810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,82 +4170,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>32967</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23039</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47783</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>40183</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>29976</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>55335</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>32967</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22903</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>47273</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>40183</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>28812</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>54341</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62013</t>
+          <t>59252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97962</t>
+          <t>98541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201106</t>
+          <t>200138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263567</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273692</t>
+          <t>277503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346064</t>
+          <t>347318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3300602</t>
+          <t>3300552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3337921</t>
+          <t>3340863</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3244374</t>
+          <t>3244399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3311039</t>
+          <t>3310572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6560626</t>
+          <t>6557325</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6637230</t>
+          <t>6630879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>734926</t>
+          <t>735636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>746708</t>
+          <t>746714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>979229</t>
+          <t>979143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>990217</t>
+          <t>990221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1719596</t>
+          <t>1720028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1735083</t>
+          <t>1735004</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23686</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56078</t>
+          <t>56093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88820</t>
+          <t>89685</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68445</t>
+          <t>68728</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>106819</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2040605</t>
+          <t>2040640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2057541</t>
+          <t>2057134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1872381</t>
+          <t>1871347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1909043</t>
+          <t>1907852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3923161</t>
+          <t>3919116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3961252</t>
+          <t>3960521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26598</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531590</t>
+          <t>531077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>542119</t>
+          <t>542089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>504479</t>
+          <t>504439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>526778</t>
+          <t>526979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1042552</t>
+          <t>1041915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1066031</t>
+          <t>1066605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31601</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42216</t>
+          <t>43603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85478</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124973</t>
+          <t>124976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111670</t>
+          <t>111813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157032</t>
+          <t>158328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3317953</t>
+          <t>3317796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3341165</t>
+          <t>3340704</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3374626</t>
+          <t>3373886</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3417166</t>
+          <t>3417465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6704871</t>
+          <t>6701379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6753829</t>
+          <t>6750521</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>43062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47137</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1018823</t>
+          <t>1017719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1028994</t>
+          <t>1028879</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1271545</t>
+          <t>1271361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1293788</t>
+          <t>1294188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2296635</t>
+          <t>2295227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2320475</t>
+          <t>2320585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137240</t>
+          <t>139138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186449</t>
+          <t>187637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166324</t>
+          <t>166464</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>219428</t>
+          <t>219857</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1642330</t>
+          <t>1640928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1665900</t>
+          <t>1665550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1392522</t>
+          <t>1392492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1442646</t>
+          <t>1441186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3044188</t>
+          <t>3043981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3099511</t>
+          <t>3100061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>30721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48505</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76688</t>
+          <t>76968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64424</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101270</t>
+          <t>100299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>518763</t>
+          <t>518777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>538787</t>
+          <t>539105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398331</t>
+          <t>396918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>427278</t>
+          <t>427078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>923703</t>
+          <t>922164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>960657</t>
+          <t>959384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71108</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>222005</t>
+          <t>223995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>284702</t>
+          <t>286479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274280</t>
+          <t>270478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343549</t>
+          <t>336891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3192980</t>
+          <t>3194420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3226611</t>
+          <t>3226769</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3080756</t>
+          <t>3079454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3144442</t>
+          <t>3144532</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6287354</t>
+          <t>6294006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6360052</t>
+          <t>6363882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41271</t>
+          <t>41433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58069</t>
+          <t>57725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>945225</t>
+          <t>945304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>961071</t>
+          <t>961394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1285972</t>
+          <t>1284954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1309346</t>
+          <t>1310025</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2240123</t>
+          <t>2239797</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2267237</t>
+          <t>2266905</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,47 +3258,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18981</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11841</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30322</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18981</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29726</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38042</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>32225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60279</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117084</t>
+          <t>117211</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>162481</t>
+          <t>160650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157796</t>
+          <t>156400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>212601</t>
+          <t>210700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1888551</t>
+          <t>1890101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1918939</t>
+          <t>1918847</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1568995</t>
+          <t>1569189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1617679</t>
+          <t>1616789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3467840</t>
+          <t>3468458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3526341</t>
+          <t>3527881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80817</t>
+          <t>81408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65744</t>
+          <t>64596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103734</t>
+          <t>103052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>450208</t>
+          <t>449036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469441</t>
+          <t>468715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366524</t>
+          <t>365747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400603</t>
+          <t>398083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>824318</t>
+          <t>824007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>861810</t>
+          <t>863681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29976</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55335</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59252</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98541</t>
+          <t>96371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200138</t>
+          <t>201503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>262001</t>
+          <t>265307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277503</t>
+          <t>275757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347318</t>
+          <t>348942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3300552</t>
+          <t>3302291</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3340863</t>
+          <t>3338748</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3244399</t>
+          <t>3242053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3310572</t>
+          <t>3310491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6557325</t>
+          <t>6559649</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6630879</t>
+          <t>6633415</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>735636</t>
+          <t>734931</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>746714</t>
+          <t>746684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>979143</t>
+          <t>979801</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>990221</t>
+          <t>990035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1720028</t>
+          <t>1720536</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1735004</t>
+          <t>1735090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>55301</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>87451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68728</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106819</t>
+          <t>105967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2040640</t>
+          <t>2040304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2057134</t>
+          <t>2057355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1871347</t>
+          <t>1873626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1907852</t>
+          <t>1909357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3919116</t>
+          <t>3920959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3960521</t>
+          <t>3962764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>42413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49965</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531077</t>
+          <t>531610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>542089</t>
+          <t>542104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>504439</t>
+          <t>503437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>526979</t>
+          <t>526099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1041915</t>
+          <t>1042701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1066605</t>
+          <t>1066154</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28468</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>32110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43603</t>
+          <t>41888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85439</t>
+          <t>86545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124976</t>
+          <t>126204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111813</t>
+          <t>114071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158328</t>
+          <t>158086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3317796</t>
+          <t>3318807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3340704</t>
+          <t>3340827</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3373886</t>
+          <t>3373234</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3417465</t>
+          <t>3415907</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6701379</t>
+          <t>6703466</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6750521</t>
+          <t>6750288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
